--- a/data/trans_dic/IP07_C15_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C15_2023-Edad-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 92,89%)</t>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 15,36</t>
+          <t>4,83; 15,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 15,79</t>
+          <t>4,03; 15,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 13,83</t>
+          <t>5,86; 13,84</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 18,53</t>
+          <t>7,05; 17,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 18,47</t>
+          <t>9,18; 19,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,02; 16,26</t>
+          <t>9,08; 17,03</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 15,25</t>
+          <t>7,5; 15,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 16,06</t>
+          <t>8,34; 16,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,19</t>
+          <t>8,61; 13,98</t>
         </is>
       </c>
     </row>
@@ -723,18 +723,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 92,89%)</t>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>14581</t>
         </is>
       </c>
     </row>
@@ -828,17 +828,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2581; 10126</t>
+          <t>4427; 14049</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5056; 14583</t>
+          <t>2803; 11042</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8899; 21897</t>
+          <t>9450; 22320</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15710</t>
+          <t>17788</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>16041</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34882</t>
+          <t>33829</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7764; 24618</t>
+          <t>11045; 27296</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11444; 29181</t>
+          <t>10630; 23009</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23342; 47307</t>
+          <t>24747; 46416</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49633</t>
+          <t>48409</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11854; 30319</t>
+          <t>18627; 37449</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19212; 40210</t>
+          <t>15458; 30076</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36702; 63756</t>
+          <t>37331; 60644</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP07_C15_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C15_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,239 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4,83; 15,32</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4,03; 15,88</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5,86; 13,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12,41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7,05; 17,42</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9,18; 19,86</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9,08; 17,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>7,5; 15,08</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8,34; 16,22</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8,61; 13,98</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A6:A7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -777,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.09461119248605597</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.08489012983802044</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.09041878222196337</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>8677</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14581</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.04826469834306201</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.04030997109245735</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.05859994953526346</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4427; 14049</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2803; 11042</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9450; 22320</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.153186416548821</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1587682627356809</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1384102391812944</v>
       </c>
     </row>
     <row r="7">
@@ -850,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1135382902188046</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.138455200812155</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1241309123376927</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>17788</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>16041</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33829</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.07049774577106942</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.09175146173447767</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.09080531317171239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>11045; 27296</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10630; 23009</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>24747; 46416</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.174227122605341</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1986054889464357</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1703179464071268</v>
       </c>
     </row>
     <row r="10">
@@ -923,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1065495886581912</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1183621320570187</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1115983309592058</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>26465</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>21944</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>48409</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.07499174689289642</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.08337657299074749</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.08605981245352706</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>18627; 37449</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>15458; 30076</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37331; 60644</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1507715250547991</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1622219595541471</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1398032517546698</v>
       </c>
     </row>
     <row r="13">
@@ -1004,4 +725,303 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>8677</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>5904</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>14581</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>4427</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2803</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>9450</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>14049</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>11042</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>22320</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>17788</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>16041</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>33829</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>11045</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>10630</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>24747</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>27296</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>23009</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>46416</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>26465</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>21944</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>48409</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>18627</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>15458</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>37331</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>37449</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>30076</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>60644</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A12:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>